--- a/lessons/gallery/excels/remarks_lcs_star.xlsx
+++ b/lessons/gallery/excels/remarks_lcs_star.xlsx
@@ -162,12 +162,12 @@
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
-        <t>-Tab (12:31:12.499), +tab (00:00:00)</t>
+        <t>-Tab (12:31:12.499) ~0.67, +tab (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317), -Karelia (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -b (13:21:26.040), -) (13:21:26.405), -; (13:21:26.744), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -Karelia (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -} (13:32:11.409), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:22.736), +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +! (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
+        <t>-Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -b (13:21:26.040), -) (13:21:26.405), -; (13:21:26.744), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -} (13:32:11.409) ~1.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:22.736) ~0.83, +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +! (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -187,12 +187,12 @@
     </comment>
     <comment ref="M5" authorId="0" shapeId="0">
       <text>
-        <t>-JavaScript (12:24:24.306), +Javascript (00:00:00)</t>
+        <t>-JavaScript (12:24:24.306) ~0.90, +Javascript (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
       <text>
-        <t>-myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -Karelia (12:46:59.354), -Karelia (13:28:16.030), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
+        <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Karelia (12:46:59.354) ~0.86, -Karelia (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D12" authorId="0" shapeId="0">
@@ -217,12 +217,12 @@
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
-        <t>-abbreviations (12:29:01.416), +abbreaviations (00:00:00)</t>
+        <t>-abbreviations (12:29:01.416) ~0.93, +abbreaviations (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317), -Max (13:05:08.613), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549), +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
+        <t>-Karelia (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -242,12 +242,12 @@
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:24:11.928), -boilerplate (12:30:45.202), +boilerpate (00:00:00)</t>
+        <t>-! (12:24:11.928), -boilerplate (12:30:45.202) ~0.91, +boilerpate (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223), -. (13:19:44.184), -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168), -` (13:32:14.220), -Weekend (13:37:10.693), +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223) ~0.86, -. (13:19:44.184) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -Weekend (13:37:10.693) ~0.00, +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -267,12 +267,12 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-: (12:29:02.589), -followed (12:31:10.973), +( (00:00:00), +folowed (00:00:00), +) (00:00:00)</t>
+        <t>-: (12:29:02.589), -followed (12:31:10.973) ~0.88, +( (00:00:00), +folowed (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -, (12:38:28.542), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -, (12:41:18.113), -oppositeBoolean (12:41:21.351), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -) (13:23:22.089), -; (13:23:22.313), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +oppositeBoolean (00:00:00), +, (00:00:00), +oppositeBoolean (00:00:00), +, (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
+        <t>-study (12:35:31.258) ~0.57, -at (12:35:31.858) ~0.50, -Karelia (12:35:33.317), -, (12:38:28.542) ~1.00, -oppositeBoolean (12:38:31.842) ~1.00, -; (12:38:32.588), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -, (12:41:18.113) ~1.00, -oppositeBoolean (12:41:21.351) ~1.00, -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754), -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -) (13:23:22.089), -; (13:23:22.313), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759) ~0.00, -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406) ~1.00, -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~1.00, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:15.696) ~1.00, -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +oppositeBoolean (00:00:00), +, (00:00:00), +oppositeBoolean (00:00:00), +, (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -292,12 +292,12 @@
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), +lesson (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.83, +lesson (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077), -" (13:07:52.850), -" (13:07:53.974), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -" (13:29:15.871), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +" (00:00:00), +' (00:00:00), +Karelia (00:00:00), +' (00:00:00), +! (00:00:00), +' (00:00:00), +! (00:00:00), +' (00:00:00), +) (00:00:00)</t>
+        <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077) ~0.75, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526) ~0.00, -' (13:28:26.250) ~1.00, -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981) ~1.00, -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -" (13:29:15.871) ~1.00, -! (13:29:39.865) ~1.00, -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +" (00:00:00), +' (00:00:00), +Karelia (00:00:00), +' (00:00:00), +! (00:00:00), +' (00:00:00), +! (00:00:00), +' (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E25" authorId="0" shapeId="0">
@@ -317,12 +317,12 @@
     </comment>
     <comment ref="M25" authorId="0" shapeId="0">
       <text>
-        <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), +javascript (00:00:00), +lesson (00:00:00), +Id (00:00:00), +my (00:00:00), +emmet (00:00:00), +html (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+        <t>-JavaScript (12:24:24.306) ~0.80, -Lesson (12:24:25.593) ~0.83, -id (12:27:55.052) ~0.50, -My (12:28:56.380) ~0.50, -Emmet (12:28:58.636) ~0.80, -HTML (12:30:43.236) ~0.00, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +javascript (00:00:00), +lesson (00:00:00), +Id (00:00:00), +my (00:00:00), +emmet (00:00:00), +html (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871) ~1.00, -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -342,12 +342,12 @@
     </comment>
     <comment ref="M30" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -boilerplate (12:30:45.202), +lesson (00:00:00), +boilerdplate (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.83, -boilerplate (12:30:45.202) ~0.92, +lesson (00:00:00), +boilerdplate (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:47:19.402), -` (13:31:57.168), -` (13:32:14.220), +' (00:00:00), +' (00:00:00)</t>
+        <t>-; (12:47:19.402), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, +' (00:00:00), +' (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -367,12 +367,12 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-/ (12:27:55.202), -div (12:27:55.232), -&gt; (12:27:55.242), -ordered (12:31:02.226), -Tab (12:31:12.499), -&lt; (13:09:16.821), -" (13:09:20.914), -" (13:09:20.924), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +orddr (00:00:00), +tab (00:00:00)</t>
+        <t>-/ (12:27:55.202), -div (12:27:55.232), -&gt; (12:27:55.242), -ordered (12:31:02.226) ~0.57, -Tab (12:31:12.499) ~0.67, -&lt; (13:09:16.821), -" (13:09:20.914), -" (13:09:20.924), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +orddr (00:00:00), +tab (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
-        <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077), -; (13:32:15.376), -} (13:35:58.376), -; (13:36:32.278), -; (13:36:46.343), -break (13:38:10.544), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +} (00:00:00)</t>
+        <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077) ~0.50, -; (13:32:15.376), -} (13:35:58.376) ~1.00, -; (13:36:32.278), -; (13:36:46.343), -break (13:38:10.544), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -392,12 +392,12 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -script (12:32:52.085), -https (13:09:28.845), +utf (00:00:00), +- (00:00:00), +Javascript (00:00:00), +lesson (00:00:00), +tab (00:00:00), +html (00:00:00)</t>
+        <t>-! (12:24:11.928), -UTF (12:24:12.488) ~0.00, -= (12:24:13.188) ~0.00, -JavaScript (12:24:24.306) ~0.90, -Lesson (12:24:25.593) ~0.83, -/ (12:29:39.313), -Tab (12:31:12.499) ~0.67, -script (12:32:52.085) ~1.00, -https (13:09:28.845) ~0.40, +utf (00:00:00), +- (00:00:00), +Javascript (00:00:00), +lesson (00:00:00), +tab (00:00:00), +html (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:35:33.317), -undefined (12:43:17.799), -; (12:47:19.402), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +! (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +script (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -; (12:47:19.402), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250), -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +! (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +script (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E41" authorId="0" shapeId="0">
@@ -417,12 +417,12 @@
     </comment>
     <comment ref="M41" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -&lt; (12:29:39.303), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +javaScript (00:00:00), +lesson (00:00:00), +ENter (00:00:00), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +mynumber (00:00:00), +/ (00:00:00), +/ (00:00:00), +never (00:00:00), +define (00:00:00), +without (00:00:00), +const (00:00:00), +, (00:00:00), +let (00:00:00), +( (00:00:00), +or (00:00:00), +var (00:00:00), +) (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +/ (00:00:00), +/ (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +/ (00:00:00), +/ (00:00:00), +zero (00:00:00), +is (00:00:00), +" (00:00:00), +falsy (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +array (00:00:00), +are (00:00:00), +like (00:00:00), +python (00:00:00), +lists (00:00:00), +/ (00:00:00), +/ (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +Error (00:00:00), +! (00:00:00), +Program (00:00:00), +would (00:00:00), +fail (00:00:00), +here (00:00:00), +! (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +myArray (00:00:00), +) (00:00:00), +; (00:00:00), +/ (00:00:00), +/ (00:00:00), +object (00:00:00), +are (00:00:00), +like (00:00:00), +python (00:00:00), +dictionaries (00:00:00), +' (00:00:00), +' (00:00:00), +Black (00:00:00), +Brown (00:00:00), +Kaali (00:00:00), +, (00:00:00), +Black (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +operators (00:00:00), +/ (00:00:00), +/ (00:00:00), +concatenation (00:00:00), +; (00:00:00), +a (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +a (00:00:00), +) (00:00:00), ++ (00:00:00), +5 (00:00:00), +; (00:00:00)</t>
+        <t>-&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306) ~0.90, -Lesson (12:24:25.593) ~0.83, -&lt; (12:27:55.192), -/ (12:27:55.202), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -&lt; (12:29:39.303), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293) ~0.80, -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +javaScript (00:00:00), +lesson (00:00:00), +ENter (00:00:00), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +mynumber (00:00:00), +/ (00:00:00), +/ (00:00:00), +never (00:00:00), +define (00:00:00), +without (00:00:00), +const (00:00:00), +, (00:00:00), +let (00:00:00), +( (00:00:00), +or (00:00:00), +var (00:00:00), +) (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +/ (00:00:00), +/ (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +/ (00:00:00), +/ (00:00:00), +zero (00:00:00), +is (00:00:00), +" (00:00:00), +falsy (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +array (00:00:00), +are (00:00:00), +like (00:00:00), +python (00:00:00), +lists (00:00:00), +/ (00:00:00), +/ (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +Error (00:00:00), +! (00:00:00), +Program (00:00:00), +would (00:00:00), +fail (00:00:00), +here (00:00:00), +! (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +myArray (00:00:00), +) (00:00:00), +; (00:00:00), +/ (00:00:00), +/ (00:00:00), +object (00:00:00), +are (00:00:00), +like (00:00:00), +python (00:00:00), +dictionaries (00:00:00), +' (00:00:00), +' (00:00:00), +Black (00:00:00), +Brown (00:00:00), +Kaali (00:00:00), +, (00:00:00), +Black (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +operators (00:00:00), +/ (00:00:00), +/ (00:00:00), +concatenation (00:00:00), +; (00:00:00), +a (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +a (00:00:00), +) (00:00:00), ++ (00:00:00), +5 (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O41" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -, (13:11:01.803), -black (13:11:11.856), -appendChild (13:13:30.342), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -console (13:22:40.955), -. (13:22:41.160), -log (13:22:41.756), -( (13:22:42.069), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676) ~0.88, -myString (12:35:43.276) ~0.62, -= (12:36:44.740), -! (12:36:45.837) ~0.00, -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842) ~0.47, -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226) ~1.00, -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -, (13:11:01.803) ~1.00, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -console (13:22:40.955), -. (13:22:41.160), -log (13:22:41.756), -( (13:22:42.069), -; (13:25:51.456) ~1.00, -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002) ~1.00, -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226) ~1.00, -console (13:34:46.231) ~1.00, -. (13:34:46.485) ~1.00, -log (13:34:47.116) ~1.00, -( (13:34:47.310) ~1.00, -today (13:34:48.450) ~0.29, -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041) ~1.00, -; (13:34:51.441) ~1.00, -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -442,12 +442,12 @@
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
       <text>
-        <t>-first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), +First (00:00:00), +Emnet (00:00:00), +abbbriviations (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
+        <t>-first (12:28:57.481) ~0.80, -Emmet (12:28:58.636) ~0.80, -abbreviations (12:29:01.416) ~0.86, -ol (12:29:38.973) ~0.50, -/ (12:29:39.313), -ol (12:29:39.333) ~0.50, -ol (12:30:53.144) ~0.50, +First (00:00:00), +Emnet (00:00:00), +abbbriviations (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -switch (13:35:50.520), +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +swtich (00:00:00)</t>
+        <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250), -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +swtich (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
@@ -467,12 +467,12 @@
     </comment>
     <comment ref="M45" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), +viewpoint (00:00:00), +abbreviation (00:00:00), +orderlist (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, -abbreviations (12:29:01.416) ~0.92, -ordered (12:31:02.226), -list (12:31:03.447) ~0.44, +viewpoint (00:00:00), +abbreviation (00:00:00), +orderlist (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O45" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250), -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
@@ -492,12 +492,12 @@
     </comment>
     <comment ref="M46" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -HTML (12:30:43.236), +Lession (00:00:00), +Html (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.86, -HTML (12:30:43.236) ~0.25, +Lession (00:00:00), +Html (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -; (13:25:51.456), -; (13:25:57.609), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -years (13:31:05.818), -default (13:37:00.967), +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
+        <t>-Karelia (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -; (13:25:51.456), -; (13:25:57.609), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
@@ -517,12 +517,12 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), +Viewport (00:00:00), +intial (00:00:00), +lesson (00:00:00), +order (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.88, -initial (12:24:13.118) ~0.86, -Lesson (12:24:25.593) ~0.83, -/ (12:29:39.313), -ordered (12:31:02.226) ~0.71, +Viewport (00:00:00), +intial (00:00:00), +lesson (00:00:00), +order (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-Charlie (13:07:39.223), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -Number (13:24:27.105), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -Karelia (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678), +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
+        <t>-Charlie (13:07:39.223) ~0.86, -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -Karelia (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -542,12 +542,12 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -Enter (12:31:14.293), +viewpoint (00:00:00), +enter (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, -Enter (12:31:14.293) ~0.80, +viewpoint (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053), -default (13:37:00.967), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
+        <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053) ~0.00, -default (13:37:00.967) ~0.14, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -567,12 +567,12 @@
     </comment>
     <comment ref="M51" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -abbreviations (12:29:01.416), +Lession (00:00:00), +abbreviatios (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.86, -abbreviations (12:29:01.416) ~0.92, +Lession (00:00:00), +abbreviatios (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O51" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030), -! (13:28:30.583), -36 (13:30:50.077), +Karela (00:00:00), +! (00:00:00), +22 (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030) ~0.86, -! (13:28:30.583) ~1.00, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +! (00:00:00), +22 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
@@ -592,12 +592,12 @@
     </comment>
     <comment ref="M56" authorId="0" shapeId="0">
       <text>
-        <t>-container (12:30:48.969), -items (12:31:06.206), +containter (00:00:00), +item (00:00:00)</t>
+        <t>-container (12:30:48.969) ~0.90, -items (12:31:06.206) ~0.80, +containter (00:00:00), +item (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O56" authorId="0" shapeId="0">
       <text>
-        <t>-25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Karelia (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030), -! (13:28:16.362), -Karelia (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Karelia (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460), +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
+        <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Karelia (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~1.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
@@ -617,12 +617,12 @@
     </comment>
     <comment ref="M59" authorId="0" shapeId="0">
       <text>
-        <t>-abbreviations (12:29:01.416), +abbreviation (00:00:00)</t>
+        <t>-abbreviations (12:29:01.416) ~0.92, +abbreviation (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-Karelia (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097), +karelia (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
+        <t>-Karelia (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +karelia (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D61" authorId="0" shapeId="0">
@@ -647,17 +647,17 @@
     </comment>
     <comment ref="M61" authorId="0" shapeId="0">
       <text>
-        <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), +java (00:00:00), +script (00:00:00), +lesson (00:00:00), +First (00:00:00), +Ordered (00:00:00), +tab (00:00:00)</t>
+        <t>-JavaScript (12:24:24.306) ~0.50, -Lesson (12:24:25.593) ~0.83, -first (12:28:57.481) ~0.80, -! (12:30:40.873), -ordered (12:31:02.226) ~0.86, -Tab (12:31:12.499) ~0.67, +java (00:00:00), +script (00:00:00), +lesson (00:00:00), +First (00:00:00), +Ordered (00:00:00), +tab (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O61" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Karelia (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -; (13:19:38.607), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -Karelia (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676) ~0.57, -Karelia (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -; (13:19:38.607), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613) ~1.00, -; (13:19:50.458) ~1.00, -a (13:20:06.496) ~1.00, -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Karelia (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -677,12 +677,12 @@
     </comment>
     <comment ref="M62" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -boilerplate (12:30:45.202), -Tab (12:31:12.499), -Enter (12:31:14.293), +Lession (00:00:00), +bolierplate (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.86, -boilerplate (12:30:45.202) ~0.82, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +Lession (00:00:00), +bolierplate (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O62" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:35:38.458), -brown (13:05:24.043), -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077), -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
+        <t>-; (12:35:38.458), -brown (13:05:24.043) ~0.80, -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077) ~0.00, -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
@@ -702,12 +702,12 @@
     </comment>
     <comment ref="M66" authorId="0" shapeId="0">
       <text>
-        <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236), -ordered (12:31:02.226), +Html (00:00:00), +order (00:00:00)</t>
+        <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236) ~0.25, -ordered (12:31:02.226) ~0.71, +Html (00:00:00), +order (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
       <text>
-        <t>-oppositeBoolean (12:41:07.806), -oppositeBoolean (12:41:21.351), +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029), -log (13:19:44.775), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
+        <t>-oppositeBoolean (12:41:07.806) ~0.93, -oppositeBoolean (12:41:21.351) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029) ~0.00, -log (13:19:44.775) ~0.00, -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699) ~1.00, +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
@@ -727,12 +727,12 @@
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
-        <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -radufromfinland (13:09:39.343), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +my (00:00:00), +abbrevetion (00:00:00), +html (00:00:00), +orderd (00:00:00), +# (00:00:00), +itemes (00:00:00), +&gt; (00:00:00)</t>
+        <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306) ~0.00, -Lesson (12:24:25.593) ~0.31, -My (12:28:56.380) ~0.50, -abbreviations (12:29:01.416) ~0.77, -HTML (12:30:43.236) ~0.00, -ordered (12:31:02.226) ~0.86, -3 (12:31:04.810) ~0.00, -items (12:31:06.206) ~0.83, -&lt; (12:32:51.935), -script (12:32:51.995), -radufromfinland (13:09:39.343) ~0.93, -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +my (00:00:00), +abbrevetion (00:00:00), +html (00:00:00), +orderd (00:00:00), +# (00:00:00), +itemes (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +welcome (00:00:00), +t (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
+        <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981), -Welcome (13:29:34.675) ~0.86, -to (13:29:35.300) ~0.50, -" (13:29:36.010), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097) ~0.00, -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693) ~0.14, -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544) ~0.83, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507) ~0.83, -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +welcome (00:00:00), +t (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -752,12 +752,12 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-Lesson (12:24:25.593), -! (12:30:40.873), +" (00:00:00), +lesson (00:00:00), +/ (00:00:00)</t>
+        <t>-Lesson (12:24:25.593) ~0.83, -! (12:30:40.873), +" (00:00:00), +lesson (00:00:00), +/ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Karelia (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Karelia (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H71" authorId="0" shapeId="0">
@@ -792,12 +792,12 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-study (12:35:31.258), -Karelia (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -; (13:36:32.278), -; (13:36:54.006), -break (13:38:13.369), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
+        <t>-study (12:35:31.258) ~0.80, -Karelia (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -; (13:36:32.278), -; (13:36:54.006), -break (13:38:13.369), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
@@ -822,7 +822,7 @@
     </comment>
     <comment ref="O73" authorId="0" shapeId="0">
       <text>
-        <t>-! (13:28:30.583), -36 (13:30:50.077), +! (00:00:00), +21 (00:00:00)</t>
+        <t>-! (13:28:30.583) ~1.00, -36 (13:30:50.077) ~0.00, +! (00:00:00), +21 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
@@ -842,12 +842,12 @@
     </comment>
     <comment ref="M75" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), +view (00:00:00), +port (00:00:00), +HTMl (00:00:00), +tab (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.50, -HTML (12:30:43.236) ~0.75, -Tab (12:31:12.499) ~0.67, +view (00:00:00), +port (00:00:00), +HTMl (00:00:00), +tab (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>-myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -; (13:07:10.952), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:37.833), -" (13:29:15.871), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -break (13:38:13.369), -; (13:38:13.634), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
+        <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108) ~0.78, -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Karelia (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -; (13:07:10.952), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223) ~0.86, -" (13:07:39.689), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -; (13:28:37.833) ~1.00, -" (13:29:15.871) ~1.00, -\ (13:29:35.759) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -break (13:38:13.369), -; (13:38:13.634), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -862,12 +862,12 @@
     </comment>
     <comment ref="M78" authorId="0" shapeId="0">
       <text>
-        <t>-html (12:24:12.048), -JavaScript (12:24:24.306), -followed (12:31:10.973), +HTML (00:00:00), +" (00:00:00), +" (00:00:00), +Javascript (00:00:00), +allowed (00:00:00)</t>
+        <t>-html (12:24:12.048) ~0.00, -JavaScript (12:24:24.306) ~0.90, -followed (12:31:10.973) ~0.75, +HTML (00:00:00), +" (00:00:00), +" (00:00:00), +Javascript (00:00:00), +allowed (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
       <text>
-        <t>-log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077), -Monday (13:36:18.214), -; (13:38:17.969), +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
+        <t>-log (12:35:41.570) ~0.67, -oppositeBoolean (12:36:43.817) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077) ~0.50, -Monday (13:36:18.214) ~0.86, -; (13:38:17.969) ~0.00, +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E79" authorId="0" shapeId="0">
@@ -887,12 +887,12 @@
     </comment>
     <comment ref="M79" authorId="0" shapeId="0">
       <text>
-        <t>-ol (12:30:53.144), -all (12:31:09.440), +old (00:00:00), +All (00:00:00)</t>
+        <t>-ol (12:30:53.144) ~0.67, -all (12:31:09.440) ~0.67, +old (00:00:00), +All (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O79" authorId="0" shapeId="0">
       <text>
-        <t>-; (13:05:06.814), -% (13:22:03.842), -! (13:28:30.583), -36 (13:30:50.077), +&amp; (00:00:00), +! (00:00:00), +! (00:00:00), +31 (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00)</t>
+        <t>-; (13:05:06.814), -% (13:22:03.842) ~0.00, -! (13:28:30.583) ~1.00, -36 (13:30:50.077) ~0.50, +&amp; (00:00:00), +! (00:00:00), +! (00:00:00), +31 (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
@@ -912,12 +912,12 @@
     </comment>
     <comment ref="M81" authorId="0" shapeId="0">
       <text>
-        <t>-Tab (12:31:12.499), -Enter (12:31:14.293), +list (00:00:00), +TAB (00:00:00), +enter (00:00:00)</t>
+        <t>-Tab (12:31:12.499) ~0.33, -Enter (12:31:14.293) ~0.80, +list (00:00:00), +TAB (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O81" authorId="0" shapeId="0">
       <text>
-        <t>-ABC (12:42:20.731), -; (13:02:35.373), -Welcome (13:28:13.560), -Welcome (13:28:27.998), -Welcome (13:29:34.675), -36 (13:30:50.077), +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
+        <t>-ABC (12:42:20.731) ~0.00, -; (13:02:35.373), -Welcome (13:28:13.560) ~0.86, -Welcome (13:28:27.998) ~0.86, -Welcome (13:29:34.675) ~0.86, -36 (13:30:50.077) ~0.00, +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E82" authorId="0" shapeId="0">
@@ -937,7 +937,7 @@
     </comment>
     <comment ref="O82" authorId="0" shapeId="0">
       <text>
-        <t>-ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
+        <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
@@ -957,12 +957,12 @@
     </comment>
     <comment ref="M83" authorId="0" shapeId="0">
       <text>
-        <t>-: (12:29:02.589), -ordered (12:31:02.226), -Tab (12:31:12.499), -Enter (12:31:14.293), +; (00:00:00), +orderd (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+        <t>-: (12:29:02.589) ~0.00, -ordered (12:31:02.226) ~0.86, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +; (00:00:00), +orderd (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O83" authorId="0" shapeId="0">
       <text>
-        <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667), -Thursday (13:36:45.577), +somedate (00:00:00), +Thrusday (00:00:00)</t>
+        <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667) ~0.88, -Thursday (13:36:45.577) ~0.75, +somedate (00:00:00), +Thrusday (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-Tab (12:31:12.499), +tab (00:00:00)</t>
+          <t>-Tab (12:31:12.499) ~0.67, +tab (00:00:00)</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317), -Karelia (12:46:59.354), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:09.716), -b (13:21:26.040), -) (13:21:26.405), -; (13:21:26.744), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -Karelia (13:29:38.066), -36 (13:30:50.077), -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881), -` (13:31:57.168), -} (13:32:11.409), -` (13:32:14.220), -; (13:33:31.713), -August (13:33:55.549), -Wednesday (13:36:38.686), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:22.736), +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +! (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
+          <t>-Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.90, -; (13:20:09.716), -b (13:21:26.040), -) (13:21:26.405), -; (13:21:26.744), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -. (13:30:58.396), -log (13:30:59.108), -old (13:31:06.881) ~0.75, -` (13:31:57.168) ~0.00, -} (13:32:11.409) ~1.00, -` (13:32:14.220) ~0.00, -; (13:33:31.713), -August (13:33:55.549) ~0.83, -Wednesday (13:36:38.686) ~0.89, -Friday (13:36:53.097) ~0.83, -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:22.736) ~0.83, +const (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +charlie (00:00:00), +anotherdog (00:00:00), +coneole (00:00:00), +Wwlcome (00:00:00), +KArelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +! (00:00:00), +karelia (00:00:00), +22 (00:00:00), +pold (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00), +wednesday (00:00:00), +friday (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-JavaScript (12:24:24.306), +Javascript (00:00:00)</t>
+          <t>-JavaScript (12:24:24.306) ~0.90, +Javascript (00:00:00)</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -Karelia (12:46:59.354), -Karelia (13:28:16.030), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
+          <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -Karelia (12:46:59.354) ~0.86, -Karelia (13:28:16.030) ~0.86, -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -` (13:31:57.168), -` (13:32:14.220), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-abbreviations (12:29:01.416), +abbreaviations (00:00:00)</t>
+          <t>-abbreviations (12:29:01.416) ~0.93, +abbreaviations (00:00:00)</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317), -Max (13:05:08.613), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -Welcome (13:28:13.560), -Date (13:33:53.451), -August (13:33:55.549), +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
+          <t>-Karelia (12:35:33.317) ~0.86, -Max (13:05:08.613) ~0.67, -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -Welcome (13:28:13.560) ~0.86, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +karelia (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +max (00:00:00), +welcome (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-! (12:24:11.928), -boilerplate (12:30:45.202), +boilerpate (00:00:00)</t>
+          <t>-! (12:24:11.928), -boilerplate (12:30:45.202) ~0.91, +boilerpate (00:00:00)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223), -. (13:19:44.184), -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168), -` (13:32:14.220), -Weekend (13:37:10.693), +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -Charlie (13:07:39.223) ~0.86, -. (13:19:44.184) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -Weekend (13:37:10.693) ~0.00, +am (00:00:00), +Charle (00:00:00), +, (00:00:00), +a (00:00:00), += (00:00:00), +" (00:00:00), +5 (00:00:00), +" (00:00:00), +; (00:00:00), +b (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +a (00:00:00), ++ (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-: (12:29:02.589), -followed (12:31:10.973), +( (00:00:00), +folowed (00:00:00), +) (00:00:00)</t>
+          <t>-: (12:29:02.589), -followed (12:31:10.973) ~0.88, +( (00:00:00), +folowed (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-study (12:35:31.258), -at (12:35:31.858), -Karelia (12:35:33.317), -, (12:38:28.542), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -, (12:41:18.113), -oppositeBoolean (12:41:21.351), -; (13:05:06.814), -" (13:05:08.095), -Max (13:05:08.613), -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524), -" (13:05:23.089), -" (13:05:24.754), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -" (13:07:52.850), -" (13:07:53.974), -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437), -" (13:20:07.578), -" (13:20:08.157), -; (13:22:53.102), -) (13:23:22.089), -; (13:23:22.313), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -someDate (13:33:51.019), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Thursday (13:36:45.577), -Weekend (13:37:10.693), -; (13:38:10.869), -; (13:38:15.696), -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +oppositeBoolean (00:00:00), +, (00:00:00), +oppositeBoolean (00:00:00), +, (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
+          <t>-study (12:35:31.258) ~0.57, -at (12:35:31.858) ~0.50, -Karelia (12:35:33.317), -, (12:38:28.542) ~1.00, -oppositeBoolean (12:38:31.842) ~1.00, -; (12:38:32.588), -myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -, (12:41:18.113) ~1.00, -oppositeBoolean (12:41:21.351) ~1.00, -; (13:05:06.814), -" (13:05:08.095) ~0.00, -Max (13:05:08.613) ~0.67, -" (13:05:08.847), -" (13:05:18.869), -" (13:05:20.541), -eyes (13:05:22.524) ~0.75, -" (13:05:23.089) ~0.00, -" (13:05:24.754), -" (13:07:37.700) ~0.00, -Charlie (13:07:39.223) ~0.71, -" (13:07:39.689) ~0.00, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -" (13:10:58.977), -" (13:11:00.402), -" (13:11:05.379), -" (13:11:09.329), -" (13:11:10.342), -" (13:11:12.437) ~0.00, -" (13:20:07.578) ~0.00, -" (13:20:08.157) ~0.00, -; (13:22:53.102), -) (13:23:22.089), -; (13:23:22.313), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759) ~0.00, -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406) ~1.00, -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -someDate (13:33:51.019) ~0.75, -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -someDate (13:34:04.667) ~0.75, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.71, -Thursday (13:36:45.577) ~1.00, -Weekend (13:37:10.693) ~0.86, -; (13:38:10.869), -; (13:38:15.696) ~1.00, -; (13:38:17.969), -; (13:38:20.534), -; (13:38:23.026), +am (00:00:00), +studing (00:00:00), +oppositeBoolean (00:00:00), +, (00:00:00), +oppositeBoolean (00:00:00), +, (00:00:00), +' (00:00:00), +max (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +eys (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +Charley (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +. (00:00:00), +someDay (00:00:00), +' (00:00:00), +2024 (00:00:00), +- (00:00:00), +03 (00:00:00), +- (00:00:00), +10 (00:00:00), +' (00:00:00), +someDay (00:00:00), +monday (00:00:00), +tusday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Wednesday (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Thursday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +break (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), +lesson (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.83, +lesson (00:00:00)</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077), -" (13:07:52.850), -" (13:07:53.974), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -" (13:29:15.871), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +" (00:00:00), +' (00:00:00), +Karelia (00:00:00), +' (00:00:00), +! (00:00:00), +' (00:00:00), +! (00:00:00), +' (00:00:00), +) (00:00:00)</t>
+          <t>-; (12:42:36.696), -; (12:52:14.599), -furr (13:05:18.077) ~0.75, -" (13:07:52.850) ~0.00, -" (13:07:53.974) ~0.00, -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526) ~0.00, -' (13:28:26.250) ~1.00, -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981) ~1.00, -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -" (13:29:15.871) ~1.00, -! (13:29:39.865) ~1.00, -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), +fur (00:00:00), +' (00:00:00), +' (00:00:00), +* (00:00:00), +" (00:00:00), +' (00:00:00), +Karelia (00:00:00), +' (00:00:00), +! (00:00:00), +' (00:00:00), +! (00:00:00), +' (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593), -id (12:27:55.052), -My (12:28:56.380), -Emmet (12:28:58.636), -HTML (12:30:43.236), -Tab (12:31:12.499), -Enter (12:31:14.293), +javascript (00:00:00), +lesson (00:00:00), +Id (00:00:00), +my (00:00:00), +emmet (00:00:00), +html (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+          <t>-JavaScript (12:24:24.306) ~0.80, -Lesson (12:24:25.593) ~0.83, -id (12:27:55.052) ~0.50, -My (12:28:56.380) ~0.50, -Emmet (12:28:58.636) ~0.80, -HTML (12:30:43.236) ~0.00, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +javascript (00:00:00), +lesson (00:00:00), +Id (00:00:00), +my (00:00:00), +emmet (00:00:00), +html (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -at (12:35:31.858), -Karelia (12:35:33.317), -Karelia (12:46:59.354), -2 (12:48:52.350), -dog (13:05:03.658), -Max (13:05:08.613), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -Charlie (13:07:39.223), -dog (13:07:52.399), -Rex (13:11:00.170), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -I (13:30:59.741), -` (13:31:57.168), -I (13:32:08.777), -` (13:32:14.220), -August (13:33:55.549), -console (13:34:01.942), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -at (12:35:31.858) ~0.00, -Karelia (12:35:33.317) ~0.86, -Karelia (12:46:59.354) ~0.86, -2 (12:48:52.350) ~0.00, -dog (13:05:03.658) ~0.67, -Max (13:05:08.613) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -dog (13:07:52.399) ~0.67, -Rex (13:11:00.170) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871) ~1.00, -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -I (13:30:59.741) ~0.00, -` (13:31:57.168) ~0.00, -I (13:32:08.777) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -console (13:34:01.942) ~0.86, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.67, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.71, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +in (00:00:00), +karelia (00:00:00), +, (00:00:00), +karelia (00:00:00), +3 (00:00:00), +Dog (00:00:00), +max (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +charlie (00:00:00), +Dog (00:00:00), +rex (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +august (00:00:00), +cosole (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wendsday (00:00:00), +thursday (00:00:00), +fraiday (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -boilerplate (12:30:45.202), +lesson (00:00:00), +boilerdplate (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.83, -boilerplate (12:30:45.202) ~0.92, +lesson (00:00:00), +boilerdplate (00:00:00)</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-; (12:47:19.402), -` (13:31:57.168), -` (13:32:14.220), +' (00:00:00), +' (00:00:00)</t>
+          <t>-; (12:47:19.402), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, +' (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-/ (12:27:55.202), -div (12:27:55.232), -&gt; (12:27:55.242), -ordered (12:31:02.226), -Tab (12:31:12.499), -&lt; (13:09:16.821), -" (13:09:20.914), -" (13:09:20.924), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +orddr (00:00:00), +tab (00:00:00)</t>
+          <t>-/ (12:27:55.202), -div (12:27:55.232), -&gt; (12:27:55.242), -ordered (12:31:02.226) ~0.57, -Tab (12:31:12.499) ~0.67, -&lt; (13:09:16.821), -" (13:09:20.914), -" (13:09:20.924), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +orddr (00:00:00), +tab (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077), -; (13:32:15.376), -} (13:35:58.376), -; (13:36:32.278), -; (13:36:46.343), -break (13:38:10.544), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +} (00:00:00)</t>
+          <t>-; (13:02:35.373), -; (13:20:09.716), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -= (13:26:10.651), -; (13:26:12.162), -; (13:26:24.323), -! (13:28:16.362), -! (13:28:30.583), -36 (13:30:50.077) ~0.50, -; (13:32:15.376), -} (13:35:58.376) ~1.00, -; (13:36:32.278), -; (13:36:46.343), -break (13:38:10.544), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), -; (13:38:23.026), +35 (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-! (12:24:11.928), -UTF (12:24:12.488), -= (12:24:13.188), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -/ (12:29:39.313), -Tab (12:31:12.499), -script (12:32:52.085), -https (13:09:28.845), +utf (00:00:00), +- (00:00:00), +Javascript (00:00:00), +lesson (00:00:00), +tab (00:00:00), +html (00:00:00)</t>
+          <t>-! (12:24:11.928), -UTF (12:24:12.488) ~0.00, -= (12:24:13.188) ~0.00, -JavaScript (12:24:24.306) ~0.90, -Lesson (12:24:25.593) ~0.83, -/ (12:29:39.313), -Tab (12:31:12.499) ~0.67, -script (12:32:52.085) ~1.00, -https (13:09:28.845) ~0.40, +utf (00:00:00), +- (00:00:00), +Javascript (00:00:00), +lesson (00:00:00), +tab (00:00:00), +html (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:35:33.317), -undefined (12:43:17.799), -; (12:47:19.402), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -. (13:07:09.027), -Charlie (13:07:39.223), -anotherDog (13:10:55.220), -; (13:20:17.407), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560), -Karelia (13:28:16.030), -' (13:28:26.250), -Welcome (13:28:27.998), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -Welcome (13:29:34.675), -Karelia (13:29:38.066), -36 (13:30:50.077), -; (13:31:07.806), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -August (13:33:55.549), -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -default (13:37:00.967), -Weekend (13:37:10.693), -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +! (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +script (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:35:33.317) ~0.86, -undefined (12:43:17.799) ~0.75, -; (12:47:19.402), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -. (13:07:09.027) ~0.00, -Charlie (13:07:39.223) ~0.86, -anotherDog (13:10:55.220) ~0.91, -; (13:20:17.407), -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Welcome (13:28:13.560) ~0.86, -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250), -Welcome (13:28:27.998) ~0.86, -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -Welcome (13:29:34.675) ~0.86, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -August (13:33:55.549) ~0.83, -; (13:34:00.044), -; (13:34:05.226), -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.62, -Friday (13:36:53.097) ~0.83, -default (13:37:00.967) ~0.88, -Weekend (13:37:10.693) ~0.71, -break (13:38:10.544), -; (13:38:10.869), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +underdefined (00:00:00), +, (00:00:00), +max (00:00:00), +, (00:00:00), +charlie (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +" (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +! (00:00:00), +welcome (00:00:00), +karelia (00:00:00), +21 (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +august (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thrusday (00:00:00), +friday (00:00:00), +defeault (00:00:00), +weekwnd (00:00:00), +script (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -&lt; (12:27:55.192), -/ (12:27:55.202), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -&lt; (12:29:39.303), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +javaScript (00:00:00), +lesson (00:00:00), +ENter (00:00:00), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +mynumber (00:00:00), +/ (00:00:00), +/ (00:00:00), +never (00:00:00), +define (00:00:00), +without (00:00:00), +const (00:00:00), +, (00:00:00), +let (00:00:00), +( (00:00:00), +or (00:00:00), +var (00:00:00), +) (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +/ (00:00:00), +/ (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +/ (00:00:00), +/ (00:00:00), +zero (00:00:00), +is (00:00:00), +" (00:00:00), +falsy (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +array (00:00:00), +are (00:00:00), +like (00:00:00), +python (00:00:00), +lists (00:00:00), +/ (00:00:00), +/ (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +Error (00:00:00), +! (00:00:00), +Program (00:00:00), +would (00:00:00), +fail (00:00:00), +here (00:00:00), +! (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +myArray (00:00:00), +) (00:00:00), +; (00:00:00), +/ (00:00:00), +/ (00:00:00), +object (00:00:00), +are (00:00:00), +like (00:00:00), +python (00:00:00), +dictionaries (00:00:00), +' (00:00:00), +' (00:00:00), +Black (00:00:00), +Brown (00:00:00), +Kaali (00:00:00), +, (00:00:00), +Black (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +operators (00:00:00), +/ (00:00:00), +/ (00:00:00), +concatenation (00:00:00), +; (00:00:00), +a (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +a (00:00:00), +) (00:00:00), ++ (00:00:00), +5 (00:00:00), +; (00:00:00)</t>
+          <t>-&lt; (12:24:13.658), -/ (12:24:13.668), -body (12:24:13.708), -&gt; (12:24:13.718), -&lt; (12:24:13.738), -/ (12:24:13.748), -html (12:24:13.788), -&gt; (12:24:13.798), -JavaScript (12:24:24.306) ~0.90, -Lesson (12:24:25.593) ~0.83, -&lt; (12:27:55.192), -/ (12:27:55.202), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -&lt; (12:29:39.303), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -Enter (12:31:14.293) ~0.80, -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +javaScript (00:00:00), +lesson (00:00:00), +ENter (00:00:00), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +mynumber (00:00:00), +/ (00:00:00), +/ (00:00:00), +never (00:00:00), +define (00:00:00), +without (00:00:00), +const (00:00:00), +, (00:00:00), +let (00:00:00), +( (00:00:00), +or (00:00:00), +var (00:00:00), +) (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +/ (00:00:00), +/ (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +/ (00:00:00), +/ (00:00:00), +zero (00:00:00), +is (00:00:00), +" (00:00:00), +falsy (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +array (00:00:00), +are (00:00:00), +like (00:00:00), +python (00:00:00), +lists (00:00:00), +/ (00:00:00), +/ (00:00:00), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +Error (00:00:00), +! (00:00:00), +Program (00:00:00), +would (00:00:00), +fail (00:00:00), +here (00:00:00), +! (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +myArray (00:00:00), +) (00:00:00), +; (00:00:00), +/ (00:00:00), +/ (00:00:00), +object (00:00:00), +are (00:00:00), +like (00:00:00), +python (00:00:00), +dictionaries (00:00:00), +' (00:00:00), +' (00:00:00), +Black (00:00:00), +Brown (00:00:00), +Kaali (00:00:00), +, (00:00:00), +Black (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +operators (00:00:00), +/ (00:00:00), +/ (00:00:00), +concatenation (00:00:00), +; (00:00:00), +a (00:00:00), += (00:00:00), +Number (00:00:00), +( (00:00:00), +a (00:00:00), +) (00:00:00), ++ (00:00:00), +5 (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -; (12:38:32.588), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095), -" (13:05:08.847), -black (13:05:20.120), -brown (13:05:24.043), -; (13:07:10.952), -Charlie (13:07:39.223), -, (13:11:01.803), -black (13:11:11.856), -appendChild (13:13:30.342), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -console (13:22:40.955), -. (13:22:41.160), -log (13:22:41.756), -( (13:22:42.069), -; (13:25:51.456), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676) ~0.88, -myString (12:35:43.276) ~0.62, -= (12:36:44.740), -! (12:36:45.837) ~0.00, -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842) ~0.47, -; (12:38:32.588), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226) ~1.00, -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -" (13:05:08.095) ~0.00, -" (13:05:08.847) ~0.00, -black (13:05:20.120) ~0.80, -brown (13:05:24.043) ~0.80, -; (13:07:10.952), -Charlie (13:07:39.223) ~0.43, -, (13:11:01.803) ~1.00, -black (13:11:11.856) ~0.80, -appendChild (13:13:30.342) ~0.91, -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -console (13:22:40.955), -. (13:22:41.160), -log (13:22:41.756), -( (13:22:42.069), -; (13:25:51.456) ~1.00, -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002) ~1.00, -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226) ~1.00, -console (13:34:46.231) ~1.00, -. (13:34:46.485) ~1.00, -log (13:34:47.116) ~1.00, -( (13:34:47.310) ~1.00, -today (13:34:48.450) ~0.29, -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041) ~1.00, -; (13:34:51.441) ~1.00, -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-first (12:28:57.481), -Emmet (12:28:58.636), -abbreviations (12:29:01.416), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), +First (00:00:00), +Emnet (00:00:00), +abbbriviations (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
+          <t>-first (12:28:57.481) ~0.80, -Emmet (12:28:58.636) ~0.80, -abbreviations (12:29:01.416) ~0.86, -ol (12:29:38.973) ~0.50, -/ (12:29:39.313), -ol (12:29:39.333) ~0.50, -ol (12:30:53.144) ~0.50, +First (00:00:00), +Emnet (00:00:00), +abbbriviations (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-Karelia (12:35:33.317), -; (12:35:38.458), -Karelia (12:46:59.354), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -switch (13:35:50.520), +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +swtich (00:00:00)</t>
+          <t>-Karelia (12:35:33.317) ~0.86, -; (12:35:38.458), -Karelia (12:46:59.354) ~0.86, -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:06:12.366), -; (13:07:10.952), -anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250), -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -switch (13:35:50.520) ~0.67, +karelia (00:00:00), +karelia (00:00:00), +, (00:00:00), +anotherdog (00:00:00), +anotherdog (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +swtich (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -abbreviations (12:29:01.416), -ordered (12:31:02.226), -list (12:31:03.447), +viewpoint (00:00:00), +abbreviation (00:00:00), +orderlist (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, -abbreviations (12:29:01.416) ~0.92, -ordered (12:31:02.226), -list (12:31:03.447) ~0.44, +viewpoint (00:00:00), +abbreviation (00:00:00), +orderlist (00:00:00)</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -Karelia (12:46:59.354), -Max (13:05:08.613), -Charlie (13:07:39.223), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -getDay (13:34:50.180), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -Weekend (13:37:10.693), +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.88, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -Charlie (13:07:39.223) ~0.86, -' (13:28:26.250), -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -getDay (13:34:50.180) ~0.71, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.89, -Thursday (13:36:45.577) ~0.88, -Friday (13:36:53.097) ~0.83, -Weekend (13:37:10.693) ~0.86, +mynumber (00:00:00), +mynumber (00:00:00), +karelia (00:00:00), +max (00:00:00), +Charle (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +' (00:00:00), +' (00:00:00), +august (00:00:00), +getDate (00:00:00), +tuesday (00:00:00), +wednesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +weekend (00:00:00)</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -HTML (12:30:43.236), +Lession (00:00:00), +Html (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.86, -HTML (12:30:43.236) ~0.25, +Lession (00:00:00), +Html (00:00:00)</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -; (13:25:51.456), -; (13:25:57.609), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -years (13:31:05.818), -default (13:37:00.967), +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
+          <t>-Karelia (12:46:59.354) ~0.88, +log* (12:53:22.757), -error (12:53:23.899), -furr (13:05:18.077) ~0.75, -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -; (13:25:51.456), -; (13:25:57.609), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -years (13:31:05.818) ~0.80, -default (13:37:00.967) ~0.86, +Kareliaa (00:00:00), +Furr (00:00:00), +year (00:00:00), +defult (00:00:00)</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -initial (12:24:13.118), -Lesson (12:24:25.593), -/ (12:29:39.313), -ordered (12:31:02.226), +Viewport (00:00:00), +intial (00:00:00), +lesson (00:00:00), +order (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.88, -initial (12:24:13.118) ~0.86, -Lesson (12:24:25.593) ~0.83, -/ (12:29:39.313), -ordered (12:31:02.226) ~0.71, +Viewport (00:00:00), +intial (00:00:00), +lesson (00:00:00), +order (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-Charlie (13:07:39.223), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -Number (13:24:27.105), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -Karelia (13:29:38.066), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678), +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
+          <t>-Charlie (13:07:39.223) ~0.86, -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -Karelia (13:29:38.066) ~0.86, -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +charlie (00:00:00), +Numbers (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +Karelia (00:00:00), +karelia (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -Enter (12:31:14.293), +viewpoint (00:00:00), +enter (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, -Enter (12:31:14.293) ~0.80, +viewpoint (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053), -default (13:37:00.967), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
+          <t>-; (12:35:38.458), -; (12:41:10.990), +log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053) ~0.00, -default (13:37:00.967) ~0.14, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -abbreviations (12:29:01.416), +Lession (00:00:00), +abbreviatios (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.86, -abbreviations (12:29:01.416) ~0.92, +Lession (00:00:00), +abbreviatios (00:00:00)</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030), -! (13:28:30.583), -36 (13:30:50.077), +Karela (00:00:00), +! (00:00:00), +22 (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -; (13:05:06.814), -Karelia (13:28:16.030) ~0.86, -! (13:28:30.583) ~1.00, -36 (13:30:50.077) ~0.00, +Karela (00:00:00), +! (00:00:00), +22 (00:00:00)</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>-container (12:30:48.969), -items (12:31:06.206), +containter (00:00:00), +item (00:00:00)</t>
+          <t>-container (12:30:48.969) ~0.90, -items (12:31:06.206) ~0.80, +containter (00:00:00), +item (00:00:00)</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-25 (12:33:49.617), -2 (12:33:50.650), -; (12:36:56.445), -Karelia (12:46:59.354), -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170), -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030), -! (13:28:16.362), -Karelia (13:28:30.418), -! (13:28:30.583), -" (13:29:31.463), -Karelia (13:29:38.066), -36 (13:30:50.077), -years (13:32:12.609), -; (13:32:15.376), -August (13:33:55.549), -24 (13:33:56.247), -2025 (13:33:58.460), +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
+          <t>-25 (12:33:49.617) ~0.00, -2 (12:33:50.650) ~0.00, -; (12:36:56.445), -Karelia (12:46:59.354) ~0.00, -; (12:48:18.482), -; (12:48:44.383), -; (12:48:50.236), -; (12:48:53.831), -; (13:02:35.373), -; (13:07:39.891), -Rex (13:11:00.170) ~0.67, -; (13:11:21.762), -; (13:25:51.456), -; (13:25:57.609), -; (13:26:02.451), -; (13:26:07.158), -; (13:26:12.162), -Karelia (13:28:16.030) ~0.86, -! (13:28:16.362), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -" (13:29:31.463) ~1.00, -Karelia (13:29:38.066) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:32:12.609) ~0.80, -; (13:32:15.376), -August (13:33:55.549) ~0.00, -24 (13:33:56.247) ~0.50, -2025 (13:33:58.460) ~0.50, +67 (00:00:00), +67 (00:00:00), +const (00:00:00), +Hello (00:00:00), += (00:00:00), +55 (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Hello (00:00:00), +) (00:00:00), +; (00:00:00), +4 (00:00:00), +, (00:00:00), +5 (00:00:00), +, (00:00:00), +XXX (00:00:00), +, (00:00:00), +rex (00:00:00), +a (00:00:00), +, (00:00:00), +karelia (00:00:00), +karelia (00:00:00), +' (00:00:00), +karelia (00:00:00), +" (00:00:00), +' (00:00:00), +19 (00:00:00), +Years (00:00:00), +December (00:00:00), +28 (00:00:00), +2006 (00:00:00)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>-abbreviations (12:29:01.416), +abbreviation (00:00:00)</t>
+          <t>-abbreviations (12:29:01.416) ~0.92, +abbreviation (00:00:00)</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-Karelia (12:46:59.354), -= (13:26:10.651), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097), +karelia (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
+          <t>-Karelia (12:46:59.354) ~0.86, -= (13:26:10.651), -' (13:28:26.250), -Karelia (13:28:30.418) ~1.00, -! (13:28:30.583) ~1.00, -' (13:28:30.981), -" (13:29:15.871) ~1.00, -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +karelia (00:00:00), +" (00:00:00), +Karelia (00:00:00), +! (00:00:00), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>-JavaScript (12:24:24.306), -Lesson (12:24:25.593), -first (12:28:57.481), -! (12:30:40.873), -ordered (12:31:02.226), -Tab (12:31:12.499), +java (00:00:00), +script (00:00:00), +lesson (00:00:00), +First (00:00:00), +Ordered (00:00:00), +tab (00:00:00)</t>
+          <t>-JavaScript (12:24:24.306) ~0.50, -Lesson (12:24:25.593) ~0.83, -first (12:28:57.481) ~0.80, -! (12:30:40.873), -ordered (12:31:02.226) ~0.86, -Tab (12:31:12.499) ~0.67, +java (00:00:00), +script (00:00:00), +lesson (00:00:00), +First (00:00:00), +Ordered (00:00:00), +tab (00:00:00)</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -console (12:33:56.141), -myNumber (12:33:59.949), -const (12:35:25.644), -myString (12:35:27.676), -Karelia (12:35:33.317), -! (12:42:04.755), -42 (12:42:11.528), -console (12:43:10.202), -Karelia (12:46:59.354), -Max (13:05:08.613), -appendChild (13:13:30.342), -; (13:19:38.607), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -' (13:28:26.250), -Karelia (13:28:30.418), -' (13:28:30.981), -Karelia (13:29:38.066), -years (13:32:12.609), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -console (12:33:56.141) ~0.71, -myNumber (12:33:59.949) ~0.88, -const (12:35:25.644), -myString (12:35:27.676) ~0.57, -Karelia (12:35:33.317) ~0.86, -! (12:42:04.755), -42 (12:42:11.528) ~0.67, -console (12:43:10.202) ~0.86, -Karelia (12:46:59.354) ~0.86, -Max (13:05:08.613) ~0.67, -appendChild (13:13:30.342) ~0.91, -; (13:19:38.607), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613) ~1.00, -; (13:19:50.458) ~1.00, -a (13:20:06.496) ~1.00, -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -' (13:28:26.250) ~0.00, -Karelia (13:28:30.418) ~0.86, -' (13:28:30.981) ~0.00, -Karelia (13:29:38.066) ~0.86, -years (13:32:12.609) ~0.80, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +mynumber (00:00:00), +consloe (00:00:00), +mynumber (00:00:00), +connstmyString (00:00:00), +karelia (00:00:00), +142 (00:00:00), +Console (00:00:00), +karelia (00:00:00), +max (00:00:00), +appendchild (00:00:00), +b (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +a (00:00:00), +, (00:00:00), +" (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +year (00:00:00)</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -boilerplate (12:30:45.202), -Tab (12:31:12.499), -Enter (12:31:14.293), +Lession (00:00:00), +bolierplate (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.86, -boilerplate (12:30:45.202) ~0.82, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +Lession (00:00:00), +bolierplate (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O62" t="n">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>-; (12:35:38.458), -brown (13:05:24.043), -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077), -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
+          <t>-; (12:35:38.458), -brown (13:05:24.043) ~0.80, -; (13:12:34.331), -; (13:28:31.528), -36 (13:30:50.077) ~0.00, -; (13:34:00.044), +brows (00:00:00), +48 (00:00:00)</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236), -ordered (12:31:02.226), +Html (00:00:00), +order (00:00:00)</t>
+          <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -HTML (12:30:43.236) ~0.25, -ordered (12:31:02.226) ~0.71, +Html (00:00:00), +order (00:00:00)</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>-oppositeBoolean (12:41:07.806), -oppositeBoolean (12:41:21.351), +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029), -log (13:19:44.775), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
+          <t>-oppositeBoolean (12:41:07.806) ~0.93, -oppositeBoolean (12:41:21.351) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029) ~0.00, -log (13:19:44.775) ~0.00, -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699) ~1.00, +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306), -Lesson (12:24:25.593), -My (12:28:56.380), -abbreviations (12:29:01.416), -HTML (12:30:43.236), -ordered (12:31:02.226), -3 (12:31:04.810), -items (12:31:06.206), -&lt; (12:32:51.935), -script (12:32:51.995), -radufromfinland (13:09:39.343), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +my (00:00:00), +abbrevetion (00:00:00), +html (00:00:00), +orderd (00:00:00), +# (00:00:00), +itemes (00:00:00), +&gt; (00:00:00)</t>
+          <t>+Document* (12:24:21.654), -JavaScript (12:24:24.306) ~0.00, -Lesson (12:24:25.593) ~0.31, -My (12:28:56.380) ~0.50, -abbreviations (12:29:01.416) ~0.77, -HTML (12:30:43.236) ~0.00, -ordered (12:31:02.226) ~0.86, -3 (12:31:04.810) ~0.00, -items (12:31:06.206) ~0.83, -&lt; (12:32:51.935), -script (12:32:51.995), -radufromfinland (13:09:39.343) ~0.93, -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +my (00:00:00), +abbrevetion (00:00:00), +html (00:00:00), +orderd (00:00:00), +# (00:00:00), +itemes (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-I (12:35:30.061), -at (12:35:31.858), -myBoolean (12:38:28.108), -Karelia (12:46:59.354), -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613), -dog (13:07:35.114), -Charlie (13:07:39.223), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -Welcome (13:28:13.560), -to (13:28:14.166), -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -! (13:28:30.583), -' (13:28:30.981), -Welcome (13:29:34.675), -to (13:29:35.300), -" (13:29:36.010), -I (13:32:08.777), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -Tuesday (13:36:31.309), -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +welcome (00:00:00), +t (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
+          <t>-I (12:35:30.061) ~0.00, -at (12:35:31.858) ~0.00, -myBoolean (12:38:28.108) ~0.89, -Karelia (12:46:59.354) ~0.86, -; (12:51:45.212), +log* (12:53:22.757), -error (12:53:23.899), -Max (13:05:08.613) ~0.67, -dog (13:07:35.114) ~0.67, -Charlie (13:07:39.223) ~0.86, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -Welcome (13:28:13.560) ~0.86, -to (13:28:14.166) ~0.50, -! (13:28:16.362), -' (13:28:26.250), -Welcome (13:28:27.998) ~0.86, -to (13:28:28.668) ~0.50, -! (13:28:30.583), -' (13:28:30.981), -Welcome (13:29:34.675) ~0.86, -to (13:29:35.300) ~0.50, -" (13:29:36.010), -I (13:32:08.777) ~0.00, -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -Tuesday (13:36:31.309) ~0.29, -3 (13:36:33.970), -Wednesday (13:36:38.686), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097) ~0.00, -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693) ~0.14, -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544) ~0.83, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507) ~0.83, -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736) ~0.83, +Radufromfinland (00:00:00), +i (00:00:00), +in (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +max (00:00:00), +gog (00:00:00), +charlie (00:00:00), +, (00:00:00), +welcome (00:00:00), +t (00:00:00), +welcome (00:00:00), +t (00:00:00), +welcome (00:00:00), +t (00:00:00), +i (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +Tu (00:00:00), +breake (00:00:00), +1 (00:00:00), +we (00:00:00), +breake (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-Lesson (12:24:25.593), -! (12:30:40.873), +" (00:00:00), +lesson (00:00:00), +/ (00:00:00)</t>
+          <t>-Lesson (12:24:25.593) ~0.83, -! (12:30:40.873), +" (00:00:00), +lesson (00:00:00), +/ (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myBoolean (12:36:27.967), -Karelia (12:46:59.354), -. (12:58:07.899), -; (13:02:35.373), -Max (13:05:08.613), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -age (13:30:48.674), -36 (13:30:50.077), -` (13:32:14.220), -; (13:32:15.376), -console (13:34:46.231), -} (13:35:58.376), -Weekend (13:37:10.693), -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -Karelia (12:46:59.354) ~0.86, -. (12:58:07.899) ~0.00, -; (13:02:35.373) ~0.00, -Max (13:05:08.613) ~0.33, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -; (13:20:09.716), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -36 (13:30:50.077) ~0.00, -` (13:32:14.220) ~0.00, -; (13:32:15.376), -console (13:34:46.231) ~0.86, -} (13:35:58.376), -Weekend (13:37:10.693) ~0.71, -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +karelia (00:00:00), +, (00:00:00), +, (00:00:00), +MAX (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +karelia (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +22 (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +weelend (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-study (12:35:31.258), -Karelia (12:35:33.317), -36 (13:30:50.077), -years (13:31:05.818), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -; (13:36:32.278), -; (13:36:54.006), -break (13:38:13.369), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
+          <t>-study (12:35:31.258) ~0.80, -Karelia (12:35:33.317) ~0.86, -36 (13:30:50.077) ~0.00, -years (13:31:05.818) ~0.80, -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -; (13:36:32.278), -; (13:36:54.006), -break (13:38:13.369), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -break (13:38:22.736), -; (13:38:23.026), +studt (00:00:00), +karelia (00:00:00), +Karelia (00:00:00), +22 (00:00:00), +year (00:00:00), +todat (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>-! (13:28:30.583), -36 (13:30:50.077), +! (00:00:00), +21 (00:00:00)</t>
+          <t>-! (13:28:30.583) ~1.00, -36 (13:30:50.077) ~0.00, +! (00:00:00), +21 (00:00:00)</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -HTML (12:30:43.236), -Tab (12:31:12.499), +view (00:00:00), +port (00:00:00), +HTMl (00:00:00), +tab (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.50, -HTML (12:30:43.236) ~0.75, -Tab (12:31:12.499) ~0.67, +view (00:00:00), +port (00:00:00), +HTMl (00:00:00), +tab (00:00:00)</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-myString (12:35:27.676), -Karelia (12:35:33.317), -myString (12:35:43.276), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -; (12:41:04.494), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799), -Karelia (12:46:59.354), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -; (13:07:10.952), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -Karelia (13:28:16.030), -' (13:28:26.250), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:37.833), -" (13:29:15.871), -\ (13:29:35.759), -Karelia (13:29:38.066), -\ (13:29:38.349), -years (13:32:12.609), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -getDay (13:35:54.315), -Monday (13:36:18.214), -Tuesday (13:36:31.309), -Wednesday (13:36:38.686), -Thursday (13:36:45.577), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -break (13:38:13.369), -; (13:38:13.634), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
+          <t>-myString (12:35:27.676) ~0.88, -Karelia (12:35:33.317) ~0.86, -myString (12:35:43.276) ~0.88, -myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108) ~0.78, -myBoolean (12:41:00.416) ~0.89, -; (12:41:04.494), -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -; (12:41:22.064), -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, -Karelia (12:46:59.354) ~0.86, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -Max (13:05:08.613) ~0.67, -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -; (13:07:10.952), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223) ~0.86, -" (13:07:39.689), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -; (13:26:07.158), -Karelia (13:28:16.030) ~0.86, -' (13:28:26.250), -Karelia (13:28:30.418) ~0.86, -! (13:28:30.583), -' (13:28:30.981), -; (13:28:37.833) ~1.00, -" (13:29:15.871) ~1.00, -\ (13:29:35.759) ~0.00, -Karelia (13:29:38.066) ~0.86, -\ (13:29:38.349) ~0.00, -years (13:32:12.609) ~0.83, -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -getDay (13:35:54.315) ~0.83, -Monday (13:36:18.214) ~0.83, -Tuesday (13:36:31.309) ~0.86, -Wednesday (13:36:38.686) ~0.44, -Thursday (13:36:45.577) ~0.50, -Friday (13:36:53.097) ~0.38, -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -break (13:38:13.369), -; (13:38:13.634), +let (00:00:00), +mystring (00:00:00), +karelia (00:00:00), +mystring (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +karelia (00:00:00), +max (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +karelia (00:00:00), +" (00:00:00), +karelia (00:00:00), +/ (00:00:00), +karelia (00:00:00), +/ (00:00:00), +; (00:00:00), +yeasrs (00:00:00), +getday (00:00:00), +monday (00:00:00), +tuesday (00:00:00), +thursday (00:00:00), +friday (00:00:00), +saturday (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>-html (12:24:12.048), -JavaScript (12:24:24.306), -followed (12:31:10.973), +HTML (00:00:00), +" (00:00:00), +" (00:00:00), +Javascript (00:00:00), +allowed (00:00:00)</t>
+          <t>-html (12:24:12.048) ~0.00, -JavaScript (12:24:24.306) ~0.90, -followed (12:31:10.973) ~0.75, +HTML (00:00:00), +" (00:00:00), +" (00:00:00), +Javascript (00:00:00), +allowed (00:00:00)</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077), -Monday (13:36:18.214), -; (13:38:17.969), +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
+          <t>-log (12:35:41.570) ~0.67, -oppositeBoolean (12:36:43.817) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -36 (13:30:50.077) ~0.50, -Monday (13:36:18.214) ~0.86, -; (13:38:17.969) ~0.00, +lig (00:00:00), +oppositeBolean (00:00:00), +26 (00:00:00), +Mondayy (00:00:00), +, (00:00:00)</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>-ol (12:30:53.144), -all (12:31:09.440), +old (00:00:00), +All (00:00:00)</t>
+          <t>-ol (12:30:53.144) ~0.67, -all (12:31:09.440) ~0.67, +old (00:00:00), +All (00:00:00)</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>-; (13:05:06.814), -% (13:22:03.842), -! (13:28:30.583), -36 (13:30:50.077), +&amp; (00:00:00), +! (00:00:00), +! (00:00:00), +31 (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00)</t>
+          <t>-; (13:05:06.814), -% (13:22:03.842) ~0.00, -! (13:28:30.583) ~1.00, -36 (13:30:50.077) ~0.50, +&amp; (00:00:00), +! (00:00:00), +! (00:00:00), +31 (00:00:00), +. (00:00:00), +getDay (00:00:00), +( (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +someDate (00:00:00)</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>-Tab (12:31:12.499), -Enter (12:31:14.293), +list (00:00:00), +TAB (00:00:00), +enter (00:00:00)</t>
+          <t>-Tab (12:31:12.499) ~0.33, -Enter (12:31:14.293) ~0.80, +list (00:00:00), +TAB (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>-ABC (12:42:20.731), -; (13:02:35.373), -Welcome (13:28:13.560), -Welcome (13:28:27.998), -Welcome (13:29:34.675), -36 (13:30:50.077), +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
+          <t>-ABC (12:42:20.731) ~0.00, -; (13:02:35.373), -Welcome (13:28:13.560) ~0.86, -Welcome (13:28:27.998) ~0.86, -Welcome (13:29:34.675) ~0.86, -36 (13:30:50.077) ~0.00, +abc (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +welcome (00:00:00), +20 (00:00:00)</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>-ABC (12:42:20.731), -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354), -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077), -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077), -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
+          <t>-ABC (12:42:20.731) ~0.00, -; (12:42:36.696), -; (12:43:22.016), -Karelia (12:46:59.354) ~0.00, -; (12:52:14.599), -; (12:57:47.239), -; (13:02:35.373), -furr (13:05:18.077) ~0.75, -; (13:12:34.331), -; (13:25:51.456), -" (13:29:13.699), -" (13:29:15.871), -36 (13:30:50.077) ~0.00, -; (13:31:07.806), -; (13:32:15.376), +BOB (00:00:00), +MARLEY (00:00:00), +fur (00:00:00), +21 (00:00:00)</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>-: (12:29:02.589), -ordered (12:31:02.226), -Tab (12:31:12.499), -Enter (12:31:14.293), +; (00:00:00), +orderd (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
+          <t>-: (12:29:02.589) ~0.00, -ordered (12:31:02.226) ~0.86, -Tab (12:31:12.499) ~0.67, -Enter (12:31:14.293) ~0.80, +; (00:00:00), +orderd (00:00:00), +tab (00:00:00), +enter (00:00:00)</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667), -Thursday (13:36:45.577), +somedate (00:00:00), +Thrusday (00:00:00)</t>
+          <t>-; (12:47:24.675), +log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667) ~0.88, -Thursday (13:36:45.577) ~0.75, +somedate (00:00:00), +Thrusday (00:00:00)</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
